--- a/src/lib/master/__fixtures__/master-excel-roundtrip.xlsx
+++ b/src/lib/master/__fixtures__/master-excel-roundtrip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bbmetalsky-my.sharepoint.com/personal/cotyc_bbrailtech_com/Documents/web-apps/Unit-Info (fleet)/src/lib/master/__fixtures__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4BD0B6D-75E0-4BE3-A4E2-C0094CB5988E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3852D08-37F4-484A-BC13-3BB7B20EB8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8535" yWindow="465" windowWidth="11325" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0 Read Me" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
     <t>exported_at</t>
   </si>
   <si>
-    <t>2026-07-31T21:00:00.000Z</t>
+    <t>2026-08-03T00:00:00.000Z</t>
   </si>
   <si>
     <t>import_semantics</t>
@@ -415,7 +415,7 @@
     <t>Industrial camera</t>
   </si>
   <si>
-    <t>Underframe / center</t>
+    <t>Front bumper / center</t>
   </si>
   <si>
     <t>VT-4200-01</t>

--- a/src/lib/master/__fixtures__/master-excel-roundtrip.xlsx
+++ b/src/lib/master/__fixtures__/master-excel-roundtrip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bbmetalsky-my.sharepoint.com/personal/cotyc_bbrailtech_com/Documents/web-apps/Unit-Info (fleet)/src/lib/master/__fixtures__/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAD9CB84-2CE5-4AAF-AAD3-CCF81093328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9421F115-629A-42A1-B793-152B07166117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,13 +20,14 @@
     <sheet name="4 Units" sheetId="5" r:id="rId5"/>
     <sheet name="5 Unit Lines (read-only)" sheetId="6" r:id="rId6"/>
     <sheet name="6 Vue Licences (read-only)" sheetId="7" r:id="rId7"/>
+    <sheet name="7 Machine Revisions" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5451" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="919">
   <si>
     <t>field</t>
   </si>
@@ -49,7 +50,7 @@
     <t>schema_version</t>
   </si>
   <si>
-    <t>master-data/2</t>
+    <t>master-data/3</t>
   </si>
   <si>
     <t>Bumped when the sheet or column contract changes.</t>
@@ -118,10 +119,10 @@
     <t>editable</t>
   </si>
   <si>
-    <t>sheets 1, 2, 3 and 4</t>
-  </si>
-  <si>
-    <t>1 Subassemblies (which subassemblies exist, and their names), 2 Parts (the master parts lists), 3 Part Variants (revision-dependent parts), 4 Units (VIN, imported serials, and which subassemblies each machine carries).</t>
+    <t>sheets 1, 2, 3, 4 and 7</t>
+  </si>
+  <si>
+    <t>1 Subassemblies (which subassemblies exist, and their names), 2 Parts (the master parts lists), 3 Part Variants (revision-dependent parts), 4 Units (VIN, imported serials, and which subassemblies each machine carries), 7 Machine Revisions (a revision for one machine only).</t>
   </si>
   <si>
     <t>how_to_add_a_subassembly</t>
@@ -1198,6 +1199,9 @@
     <t>T-18|RG:DMF-1650-F</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>T-18|RG:DMF-1650-R</t>
   </si>
   <si>
@@ -2752,6 +2756,12 @@
     <t>Not in the licence notes sheet</t>
   </si>
   <si>
+    <t>derived_master_rev</t>
+  </si>
+  <si>
+    <t>derived_subassembly</t>
+  </si>
+  <si>
     <t>DMF-1650-F-REV-E</t>
   </si>
   <si>
@@ -2771,6 +2781,9 @@
   </si>
   <si>
     <t>fit_HY</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
 </sst>
 </file>
@@ -3285,7 +3298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -3511,10 +3524,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>
@@ -3587,10 +3600,10 @@
         <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>85</v>
@@ -4353,13 +4366,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C28" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D28" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>
@@ -4505,7 +4518,7 @@
         <v>185</v>
       </c>
       <c r="P1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -6201,7 +6214,7 @@
         <v>89</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>90</v>
@@ -6210,7 +6223,7 @@
         <v>196</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6239,7 +6252,7 @@
         <v>95</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6268,7 +6281,7 @@
         <v>99</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6300,7 +6313,7 @@
         <v>197</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6329,7 +6342,7 @@
         <v>109</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6358,7 +6371,7 @@
         <v>112</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6387,7 +6400,7 @@
         <v>115</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6416,7 +6429,7 @@
         <v>119</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6445,7 +6458,7 @@
         <v>122</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -6474,7 +6487,7 @@
         <v>125</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -6503,7 +6516,7 @@
         <v>151</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -6532,7 +6545,7 @@
         <v>151</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -6561,7 +6574,7 @@
         <v>158</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6590,7 +6603,7 @@
         <v>161</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -6619,7 +6632,7 @@
         <v>161</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -6648,7 +6661,7 @@
         <v>161</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6680,7 +6693,7 @@
         <v>201</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -6712,7 +6725,7 @@
         <v>202</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -6741,7 +6754,7 @@
         <v>95</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6770,7 +6783,7 @@
         <v>99</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -6802,7 +6815,7 @@
         <v>203</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -6831,7 +6844,7 @@
         <v>109</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -6860,7 +6873,7 @@
         <v>112</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -6889,7 +6902,7 @@
         <v>115</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -6918,7 +6931,7 @@
         <v>119</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6947,7 +6960,7 @@
         <v>122</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -6976,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -7008,7 +7021,7 @@
         <v>207</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7040,7 +7053,7 @@
         <v>208</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7069,7 +7082,7 @@
         <v>95</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7098,7 +7111,7 @@
         <v>99</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7130,7 +7143,7 @@
         <v>209</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7159,7 +7172,7 @@
         <v>109</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7188,7 +7201,7 @@
         <v>112</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7217,7 +7230,7 @@
         <v>115</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -7246,7 +7259,7 @@
         <v>119</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -7275,7 +7288,7 @@
         <v>122</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -7304,7 +7317,7 @@
         <v>125</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -7336,7 +7349,7 @@
         <v>212</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -7368,7 +7381,7 @@
         <v>213</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -7397,7 +7410,7 @@
         <v>95</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -7426,7 +7439,7 @@
         <v>99</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -7458,7 +7471,7 @@
         <v>214</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -7487,7 +7500,7 @@
         <v>109</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -7516,7 +7529,7 @@
         <v>112</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -7545,7 +7558,7 @@
         <v>115</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -7574,7 +7587,7 @@
         <v>119</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -7603,7 +7616,7 @@
         <v>122</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -7632,7 +7645,7 @@
         <v>125</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -7664,7 +7677,7 @@
         <v>217</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -7696,7 +7709,7 @@
         <v>218</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -7725,7 +7738,7 @@
         <v>95</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -7754,7 +7767,7 @@
         <v>99</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -7786,7 +7799,7 @@
         <v>219</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -7815,7 +7828,7 @@
         <v>109</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -7844,7 +7857,7 @@
         <v>112</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -7873,7 +7886,7 @@
         <v>115</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -7902,7 +7915,7 @@
         <v>119</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -7931,7 +7944,7 @@
         <v>122</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -7960,7 +7973,7 @@
         <v>125</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -7992,7 +8005,7 @@
         <v>222</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -8024,7 +8037,7 @@
         <v>218</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -8053,7 +8066,7 @@
         <v>95</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -8082,7 +8095,7 @@
         <v>99</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -8114,7 +8127,7 @@
         <v>223</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -8143,7 +8156,7 @@
         <v>109</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -8172,7 +8185,7 @@
         <v>112</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -8201,7 +8214,7 @@
         <v>115</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -8230,7 +8243,7 @@
         <v>119</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -8259,7 +8272,7 @@
         <v>122</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -8288,7 +8301,7 @@
         <v>125</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -8320,7 +8333,7 @@
         <v>226</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -8352,7 +8365,7 @@
         <v>227</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -8381,7 +8394,7 @@
         <v>95</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -8410,7 +8423,7 @@
         <v>99</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -8442,7 +8455,7 @@
         <v>228</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -8471,7 +8484,7 @@
         <v>109</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -8500,7 +8513,7 @@
         <v>112</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -8529,7 +8542,7 @@
         <v>115</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -8558,7 +8571,7 @@
         <v>119</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -8587,7 +8600,7 @@
         <v>122</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -8616,7 +8629,7 @@
         <v>125</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8645,7 +8658,7 @@
         <v>151</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8674,7 +8687,7 @@
         <v>151</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8703,7 +8716,7 @@
         <v>158</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -8732,7 +8745,7 @@
         <v>161</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -8761,7 +8774,7 @@
         <v>161</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -8790,7 +8803,7 @@
         <v>161</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -8822,7 +8835,7 @@
         <v>231</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -8854,7 +8867,7 @@
         <v>232</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -8883,7 +8896,7 @@
         <v>95</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -8912,7 +8925,7 @@
         <v>99</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -8944,7 +8957,7 @@
         <v>233</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -8973,7 +8986,7 @@
         <v>109</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -9002,7 +9015,7 @@
         <v>112</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -9031,7 +9044,7 @@
         <v>115</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -9060,7 +9073,7 @@
         <v>119</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -9089,7 +9102,7 @@
         <v>122</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -9118,7 +9131,7 @@
         <v>125</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -9150,7 +9163,7 @@
         <v>236</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -9182,7 +9195,7 @@
         <v>237</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -9211,7 +9224,7 @@
         <v>95</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -9240,7 +9253,7 @@
         <v>99</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -9272,7 +9285,7 @@
         <v>238</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -9301,7 +9314,7 @@
         <v>109</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -9330,7 +9343,7 @@
         <v>112</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -9359,7 +9372,7 @@
         <v>115</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -9388,7 +9401,7 @@
         <v>119</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -9417,7 +9430,7 @@
         <v>122</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -9446,7 +9459,7 @@
         <v>125</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -9475,7 +9488,7 @@
         <v>151</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -9504,7 +9517,7 @@
         <v>151</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -9533,7 +9546,7 @@
         <v>158</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -9562,7 +9575,7 @@
         <v>161</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -9591,7 +9604,7 @@
         <v>161</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -9620,7 +9633,7 @@
         <v>161</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -9652,7 +9665,7 @@
         <v>241</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -9684,7 +9697,7 @@
         <v>242</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -9713,7 +9726,7 @@
         <v>95</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -9742,7 +9755,7 @@
         <v>99</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -9774,7 +9787,7 @@
         <v>243</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -9803,7 +9816,7 @@
         <v>109</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -9832,7 +9845,7 @@
         <v>112</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -9861,7 +9874,7 @@
         <v>115</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -9890,7 +9903,7 @@
         <v>119</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -9919,7 +9932,7 @@
         <v>122</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -9948,7 +9961,7 @@
         <v>125</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -9980,7 +9993,7 @@
         <v>246</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -10012,7 +10025,7 @@
         <v>247</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -10041,7 +10054,7 @@
         <v>95</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -10070,7 +10083,7 @@
         <v>99</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -10102,7 +10115,7 @@
         <v>248</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -10131,7 +10144,7 @@
         <v>109</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -10160,7 +10173,7 @@
         <v>112</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -10189,7 +10202,7 @@
         <v>115</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -10218,7 +10231,7 @@
         <v>119</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -10247,7 +10260,7 @@
         <v>122</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -10276,7 +10289,7 @@
         <v>125</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -10308,7 +10321,7 @@
         <v>251</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -10340,7 +10353,7 @@
         <v>252</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -10369,7 +10382,7 @@
         <v>95</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -10398,7 +10411,7 @@
         <v>99</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -10430,7 +10443,7 @@
         <v>253</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -10459,7 +10472,7 @@
         <v>109</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -10488,7 +10501,7 @@
         <v>112</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -10517,7 +10530,7 @@
         <v>115</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -10546,7 +10559,7 @@
         <v>119</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -10575,7 +10588,7 @@
         <v>122</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -10604,7 +10617,7 @@
         <v>125</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -10633,7 +10646,7 @@
         <v>151</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -10662,7 +10675,7 @@
         <v>151</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -10691,7 +10704,7 @@
         <v>158</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -10720,7 +10733,7 @@
         <v>161</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -10749,7 +10762,7 @@
         <v>161</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -10778,7 +10791,7 @@
         <v>161</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -10810,7 +10823,7 @@
         <v>256</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -10842,7 +10855,7 @@
         <v>257</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -10871,7 +10884,7 @@
         <v>95</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -10900,7 +10913,7 @@
         <v>99</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -10932,7 +10945,7 @@
         <v>258</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -10961,7 +10974,7 @@
         <v>109</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -10990,7 +11003,7 @@
         <v>112</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -11019,7 +11032,7 @@
         <v>115</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -11048,7 +11061,7 @@
         <v>119</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -11077,7 +11090,7 @@
         <v>122</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -11106,7 +11119,7 @@
         <v>125</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -11138,7 +11151,7 @@
         <v>259</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -11158,7 +11171,7 @@
         <v>130</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>108</v>
@@ -11167,7 +11180,7 @@
         <v>132</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -11196,7 +11209,7 @@
         <v>132</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -11225,7 +11238,7 @@
         <v>128</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -11254,7 +11267,7 @@
         <v>128</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -11283,7 +11296,7 @@
         <v>161</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -11312,7 +11325,7 @@
         <v>161</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -11341,7 +11354,7 @@
         <v>161</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -11373,7 +11386,7 @@
         <v>263</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -11405,7 +11418,7 @@
         <v>264</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -11434,7 +11447,7 @@
         <v>95</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -11463,7 +11476,7 @@
         <v>99</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -11495,7 +11508,7 @@
         <v>265</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -11524,7 +11537,7 @@
         <v>109</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -11553,7 +11566,7 @@
         <v>112</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -11582,7 +11595,7 @@
         <v>115</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -11611,7 +11624,7 @@
         <v>119</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -11640,7 +11653,7 @@
         <v>122</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -11669,7 +11682,7 @@
         <v>125</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -11701,7 +11714,7 @@
         <v>268</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -11733,7 +11746,7 @@
         <v>269</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -11762,7 +11775,7 @@
         <v>95</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -11791,7 +11804,7 @@
         <v>99</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -11823,7 +11836,7 @@
         <v>270</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -11852,7 +11865,7 @@
         <v>109</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -11881,7 +11894,7 @@
         <v>112</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -11910,7 +11923,7 @@
         <v>115</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -11939,7 +11952,7 @@
         <v>119</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -11968,7 +11981,7 @@
         <v>122</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -11997,7 +12010,7 @@
         <v>125</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -12029,7 +12042,7 @@
         <v>271</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -12049,7 +12062,7 @@
         <v>130</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>108</v>
@@ -12058,7 +12071,7 @@
         <v>132</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -12087,7 +12100,7 @@
         <v>132</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -12116,7 +12129,7 @@
         <v>128</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -12145,7 +12158,7 @@
         <v>128</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -12177,7 +12190,7 @@
         <v>274</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -12209,7 +12222,7 @@
         <v>275</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -12238,7 +12251,7 @@
         <v>95</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -12267,7 +12280,7 @@
         <v>99</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -12299,7 +12312,7 @@
         <v>276</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -12328,7 +12341,7 @@
         <v>109</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -12357,7 +12370,7 @@
         <v>112</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -12386,7 +12399,7 @@
         <v>115</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -12415,7 +12428,7 @@
         <v>119</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -12444,7 +12457,7 @@
         <v>122</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -12473,7 +12486,7 @@
         <v>125</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -12502,7 +12515,7 @@
         <v>161</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -12531,7 +12544,7 @@
         <v>161</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -12560,7 +12573,7 @@
         <v>161</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -12592,7 +12605,7 @@
         <v>279</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -12624,7 +12637,7 @@
         <v>280</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -12653,7 +12666,7 @@
         <v>95</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -12682,7 +12695,7 @@
         <v>99</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -12714,7 +12727,7 @@
         <v>281</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -12743,7 +12756,7 @@
         <v>109</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -12772,7 +12785,7 @@
         <v>112</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -12801,7 +12814,7 @@
         <v>115</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -12830,7 +12843,7 @@
         <v>119</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -12859,7 +12872,7 @@
         <v>122</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -12888,7 +12901,7 @@
         <v>125</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -12920,7 +12933,7 @@
         <v>282</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -12940,7 +12953,7 @@
         <v>130</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>108</v>
@@ -12949,7 +12962,7 @@
         <v>132</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -12978,7 +12991,7 @@
         <v>132</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -13007,7 +13020,7 @@
         <v>128</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -13036,7 +13049,7 @@
         <v>128</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -13068,7 +13081,7 @@
         <v>285</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
@@ -13100,7 +13113,7 @@
         <v>286</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -13129,7 +13142,7 @@
         <v>95</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -13158,7 +13171,7 @@
         <v>99</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -13190,7 +13203,7 @@
         <v>287</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
@@ -13219,7 +13232,7 @@
         <v>109</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
@@ -13248,7 +13261,7 @@
         <v>112</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
@@ -13277,7 +13290,7 @@
         <v>115</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
@@ -13306,7 +13319,7 @@
         <v>119</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
@@ -13335,7 +13348,7 @@
         <v>122</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
@@ -13364,7 +13377,7 @@
         <v>125</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
@@ -13393,7 +13406,7 @@
         <v>161</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
@@ -13422,7 +13435,7 @@
         <v>161</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
@@ -13451,7 +13464,7 @@
         <v>161</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -13483,7 +13496,7 @@
         <v>290</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -13515,7 +13528,7 @@
         <v>291</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -13544,7 +13557,7 @@
         <v>95</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -13573,7 +13586,7 @@
         <v>99</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -13605,7 +13618,7 @@
         <v>292</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -13634,7 +13647,7 @@
         <v>109</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -13663,7 +13676,7 @@
         <v>112</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -13692,7 +13705,7 @@
         <v>115</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -13721,7 +13734,7 @@
         <v>119</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -13750,7 +13763,7 @@
         <v>122</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -13779,7 +13792,7 @@
         <v>125</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -13811,7 +13824,7 @@
         <v>295</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -13843,7 +13856,7 @@
         <v>296</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -13872,7 +13885,7 @@
         <v>95</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -13901,7 +13914,7 @@
         <v>99</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -13933,7 +13946,7 @@
         <v>297</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -13962,7 +13975,7 @@
         <v>109</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -13991,7 +14004,7 @@
         <v>112</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -14020,7 +14033,7 @@
         <v>115</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -14049,7 +14062,7 @@
         <v>119</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -14078,7 +14091,7 @@
         <v>122</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -14107,7 +14120,7 @@
         <v>125</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -14136,7 +14149,7 @@
         <v>161</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -14165,7 +14178,7 @@
         <v>161</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -14194,7 +14207,7 @@
         <v>161</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -14226,7 +14239,7 @@
         <v>300</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -14258,7 +14271,7 @@
         <v>301</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -14287,7 +14300,7 @@
         <v>95</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -14316,7 +14329,7 @@
         <v>99</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -14348,7 +14361,7 @@
         <v>302</v>
       </c>
       <c r="J291" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -14377,7 +14390,7 @@
         <v>109</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -14406,7 +14419,7 @@
         <v>112</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -14435,7 +14448,7 @@
         <v>115</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -14464,7 +14477,7 @@
         <v>119</v>
       </c>
       <c r="J295" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -14493,7 +14506,7 @@
         <v>122</v>
       </c>
       <c r="J296" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -14522,7 +14535,7 @@
         <v>125</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -14551,7 +14564,7 @@
         <v>161</v>
       </c>
       <c r="J298" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -14580,7 +14593,7 @@
         <v>161</v>
       </c>
       <c r="J299" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -14609,7 +14622,7 @@
         <v>161</v>
       </c>
       <c r="J300" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -14641,7 +14654,7 @@
         <v>305</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
@@ -14673,7 +14686,7 @@
         <v>306</v>
       </c>
       <c r="J302" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
@@ -14702,7 +14715,7 @@
         <v>95</v>
       </c>
       <c r="J303" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
@@ -14731,7 +14744,7 @@
         <v>99</v>
       </c>
       <c r="J304" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
@@ -14763,7 +14776,7 @@
         <v>307</v>
       </c>
       <c r="J305" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
@@ -14792,7 +14805,7 @@
         <v>109</v>
       </c>
       <c r="J306" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
@@ -14821,7 +14834,7 @@
         <v>112</v>
       </c>
       <c r="J307" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
@@ -14850,7 +14863,7 @@
         <v>115</v>
       </c>
       <c r="J308" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
@@ -14879,7 +14892,7 @@
         <v>119</v>
       </c>
       <c r="J309" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
@@ -14908,7 +14921,7 @@
         <v>122</v>
       </c>
       <c r="J310" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
@@ -14937,7 +14950,7 @@
         <v>125</v>
       </c>
       <c r="J311" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.25">
@@ -14966,7 +14979,7 @@
         <v>161</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
@@ -14995,7 +15008,7 @@
         <v>161</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
@@ -15024,7 +15037,7 @@
         <v>161</v>
       </c>
       <c r="J314" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
@@ -15056,7 +15069,7 @@
         <v>310</v>
       </c>
       <c r="J315" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
@@ -15088,7 +15101,7 @@
         <v>311</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
@@ -15117,7 +15130,7 @@
         <v>95</v>
       </c>
       <c r="J317" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
@@ -15146,7 +15159,7 @@
         <v>99</v>
       </c>
       <c r="J318" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
@@ -15178,7 +15191,7 @@
         <v>312</v>
       </c>
       <c r="J319" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
@@ -15207,7 +15220,7 @@
         <v>109</v>
       </c>
       <c r="J320" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
@@ -15236,7 +15249,7 @@
         <v>112</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
@@ -15265,7 +15278,7 @@
         <v>115</v>
       </c>
       <c r="J322" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
@@ -15294,7 +15307,7 @@
         <v>119</v>
       </c>
       <c r="J323" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
@@ -15323,7 +15336,7 @@
         <v>122</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
@@ -15352,7 +15365,7 @@
         <v>125</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
@@ -15384,7 +15397,7 @@
         <v>315</v>
       </c>
       <c r="J326" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
@@ -15416,7 +15429,7 @@
         <v>316</v>
       </c>
       <c r="J327" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
@@ -15445,7 +15458,7 @@
         <v>95</v>
       </c>
       <c r="J328" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
@@ -15474,7 +15487,7 @@
         <v>99</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
@@ -15506,7 +15519,7 @@
         <v>317</v>
       </c>
       <c r="J330" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
@@ -15535,7 +15548,7 @@
         <v>109</v>
       </c>
       <c r="J331" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
@@ -15564,7 +15577,7 @@
         <v>112</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.25">
@@ -15593,7 +15606,7 @@
         <v>115</v>
       </c>
       <c r="J333" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.25">
@@ -15622,7 +15635,7 @@
         <v>119</v>
       </c>
       <c r="J334" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.25">
@@ -15651,7 +15664,7 @@
         <v>122</v>
       </c>
       <c r="J335" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.25">
@@ -15680,7 +15693,7 @@
         <v>125</v>
       </c>
       <c r="J336" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.25">
@@ -15709,7 +15722,7 @@
         <v>161</v>
       </c>
       <c r="J337" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.25">
@@ -15738,7 +15751,7 @@
         <v>161</v>
       </c>
       <c r="J338" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
@@ -15767,7 +15780,7 @@
         <v>161</v>
       </c>
       <c r="J339" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
@@ -15799,7 +15812,7 @@
         <v>320</v>
       </c>
       <c r="J340" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
@@ -15831,7 +15844,7 @@
         <v>321</v>
       </c>
       <c r="J341" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
@@ -15860,7 +15873,7 @@
         <v>95</v>
       </c>
       <c r="J342" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
@@ -15889,7 +15902,7 @@
         <v>99</v>
       </c>
       <c r="J343" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
@@ -15921,7 +15934,7 @@
         <v>322</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.25">
@@ -15950,7 +15963,7 @@
         <v>109</v>
       </c>
       <c r="J345" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.25">
@@ -15979,7 +15992,7 @@
         <v>112</v>
       </c>
       <c r="J346" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
@@ -16008,7 +16021,7 @@
         <v>115</v>
       </c>
       <c r="J347" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
@@ -16037,7 +16050,7 @@
         <v>119</v>
       </c>
       <c r="J348" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
@@ -16066,7 +16079,7 @@
         <v>122</v>
       </c>
       <c r="J349" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
@@ -16095,7 +16108,7 @@
         <v>125</v>
       </c>
       <c r="J350" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
@@ -16127,7 +16140,7 @@
         <v>325</v>
       </c>
       <c r="J351" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
@@ -16159,7 +16172,7 @@
         <v>326</v>
       </c>
       <c r="J352" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.25">
@@ -16188,7 +16201,7 @@
         <v>95</v>
       </c>
       <c r="J353" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.25">
@@ -16217,7 +16230,7 @@
         <v>99</v>
       </c>
       <c r="J354" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.25">
@@ -16249,7 +16262,7 @@
         <v>327</v>
       </c>
       <c r="J355" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.25">
@@ -16278,7 +16291,7 @@
         <v>109</v>
       </c>
       <c r="J356" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.25">
@@ -16307,7 +16320,7 @@
         <v>112</v>
       </c>
       <c r="J357" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.25">
@@ -16336,7 +16349,7 @@
         <v>115</v>
       </c>
       <c r="J358" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.25">
@@ -16365,7 +16378,7 @@
         <v>119</v>
       </c>
       <c r="J359" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.25">
@@ -16394,7 +16407,7 @@
         <v>122</v>
       </c>
       <c r="J360" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.25">
@@ -16423,7 +16436,7 @@
         <v>125</v>
       </c>
       <c r="J361" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.25">
@@ -16452,7 +16465,7 @@
         <v>161</v>
       </c>
       <c r="J362" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.25">
@@ -16481,7 +16494,7 @@
         <v>161</v>
       </c>
       <c r="J363" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.25">
@@ -16510,7 +16523,7 @@
         <v>161</v>
       </c>
       <c r="J364" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.25">
@@ -16542,7 +16555,7 @@
         <v>310</v>
       </c>
       <c r="J365" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.25">
@@ -16574,7 +16587,7 @@
         <v>330</v>
       </c>
       <c r="J366" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.25">
@@ -16603,7 +16616,7 @@
         <v>95</v>
       </c>
       <c r="J367" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.25">
@@ -16632,7 +16645,7 @@
         <v>99</v>
       </c>
       <c r="J368" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.25">
@@ -16664,7 +16677,7 @@
         <v>331</v>
       </c>
       <c r="J369" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
@@ -16693,7 +16706,7 @@
         <v>109</v>
       </c>
       <c r="J370" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
@@ -16722,7 +16735,7 @@
         <v>112</v>
       </c>
       <c r="J371" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.25">
@@ -16751,7 +16764,7 @@
         <v>115</v>
       </c>
       <c r="J372" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.25">
@@ -16780,7 +16793,7 @@
         <v>119</v>
       </c>
       <c r="J373" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.25">
@@ -16809,7 +16822,7 @@
         <v>122</v>
       </c>
       <c r="J374" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.25">
@@ -16838,7 +16851,7 @@
         <v>125</v>
       </c>
       <c r="J375" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.25">
@@ -16870,7 +16883,7 @@
         <v>334</v>
       </c>
       <c r="J376" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.25">
@@ -16902,7 +16915,7 @@
         <v>335</v>
       </c>
       <c r="J377" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.25">
@@ -16931,7 +16944,7 @@
         <v>95</v>
       </c>
       <c r="J378" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.25">
@@ -16960,7 +16973,7 @@
         <v>99</v>
       </c>
       <c r="J379" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
@@ -16992,7 +17005,7 @@
         <v>336</v>
       </c>
       <c r="J380" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
@@ -17021,7 +17034,7 @@
         <v>109</v>
       </c>
       <c r="J381" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.25">
@@ -17050,7 +17063,7 @@
         <v>112</v>
       </c>
       <c r="J382" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.25">
@@ -17079,7 +17092,7 @@
         <v>115</v>
       </c>
       <c r="J383" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.25">
@@ -17108,7 +17121,7 @@
         <v>119</v>
       </c>
       <c r="J384" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.25">
@@ -17137,7 +17150,7 @@
         <v>122</v>
       </c>
       <c r="J385" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
@@ -17166,7 +17179,7 @@
         <v>125</v>
       </c>
       <c r="J386" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.25">
@@ -17195,7 +17208,7 @@
         <v>151</v>
       </c>
       <c r="J387" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.25">
@@ -17224,7 +17237,7 @@
         <v>151</v>
       </c>
       <c r="J388" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.25">
@@ -17253,7 +17266,7 @@
         <v>158</v>
       </c>
       <c r="J389" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.25">
@@ -17282,7 +17295,7 @@
         <v>161</v>
       </c>
       <c r="J390" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.25">
@@ -17311,7 +17324,7 @@
         <v>161</v>
       </c>
       <c r="J391" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.25">
@@ -17340,7 +17353,7 @@
         <v>161</v>
       </c>
       <c r="J392" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.25">
@@ -17372,7 +17385,7 @@
         <v>339</v>
       </c>
       <c r="J393" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.25">
@@ -17404,7 +17417,7 @@
         <v>340</v>
       </c>
       <c r="J394" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.25">
@@ -17433,7 +17446,7 @@
         <v>95</v>
       </c>
       <c r="J395" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.25">
@@ -17462,7 +17475,7 @@
         <v>99</v>
       </c>
       <c r="J396" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.25">
@@ -17494,7 +17507,7 @@
         <v>341</v>
       </c>
       <c r="J397" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.25">
@@ -17523,7 +17536,7 @@
         <v>109</v>
       </c>
       <c r="J398" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.25">
@@ -17552,7 +17565,7 @@
         <v>112</v>
       </c>
       <c r="J399" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.25">
@@ -17581,7 +17594,7 @@
         <v>115</v>
       </c>
       <c r="J400" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.25">
@@ -17610,7 +17623,7 @@
         <v>119</v>
       </c>
       <c r="J401" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.25">
@@ -17639,7 +17652,7 @@
         <v>122</v>
       </c>
       <c r="J402" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.25">
@@ -17668,7 +17681,7 @@
         <v>125</v>
       </c>
       <c r="J403" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.25">
@@ -17700,7 +17713,7 @@
         <v>342</v>
       </c>
       <c r="J404" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.25">
@@ -17720,7 +17733,7 @@
         <v>130</v>
       </c>
       <c r="F405" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>108</v>
@@ -17729,7 +17742,7 @@
         <v>132</v>
       </c>
       <c r="J405" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.25">
@@ -17758,7 +17771,7 @@
         <v>132</v>
       </c>
       <c r="J406" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.25">
@@ -17787,7 +17800,7 @@
         <v>128</v>
       </c>
       <c r="J407" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.25">
@@ -17816,7 +17829,7 @@
         <v>128</v>
       </c>
       <c r="J408" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.25">
@@ -17848,7 +17861,7 @@
         <v>345</v>
       </c>
       <c r="J409" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.25">
@@ -17880,7 +17893,7 @@
         <v>346</v>
       </c>
       <c r="J410" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.25">
@@ -17909,7 +17922,7 @@
         <v>95</v>
       </c>
       <c r="J411" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.25">
@@ -17938,7 +17951,7 @@
         <v>99</v>
       </c>
       <c r="J412" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.25">
@@ -17970,7 +17983,7 @@
         <v>347</v>
       </c>
       <c r="J413" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.25">
@@ -17999,7 +18012,7 @@
         <v>109</v>
       </c>
       <c r="J414" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.25">
@@ -18028,7 +18041,7 @@
         <v>112</v>
       </c>
       <c r="J415" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.25">
@@ -18057,7 +18070,7 @@
         <v>115</v>
       </c>
       <c r="J416" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.25">
@@ -18086,7 +18099,7 @@
         <v>119</v>
       </c>
       <c r="J417" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.25">
@@ -18115,7 +18128,7 @@
         <v>122</v>
       </c>
       <c r="J418" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.25">
@@ -18144,7 +18157,7 @@
         <v>125</v>
       </c>
       <c r="J419" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.25">
@@ -18173,7 +18186,7 @@
         <v>161</v>
       </c>
       <c r="J420" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.25">
@@ -18202,7 +18215,7 @@
         <v>161</v>
       </c>
       <c r="J421" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.25">
@@ -18231,7 +18244,7 @@
         <v>161</v>
       </c>
       <c r="J422" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.25">
@@ -18263,7 +18276,7 @@
         <v>350</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.25">
@@ -18295,7 +18308,7 @@
         <v>351</v>
       </c>
       <c r="J424" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.25">
@@ -18324,7 +18337,7 @@
         <v>95</v>
       </c>
       <c r="J425" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.25">
@@ -18353,7 +18366,7 @@
         <v>99</v>
       </c>
       <c r="J426" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.25">
@@ -18385,7 +18398,7 @@
         <v>352</v>
       </c>
       <c r="J427" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.25">
@@ -18414,7 +18427,7 @@
         <v>109</v>
       </c>
       <c r="J428" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.25">
@@ -18443,7 +18456,7 @@
         <v>112</v>
       </c>
       <c r="J429" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.25">
@@ -18472,7 +18485,7 @@
         <v>115</v>
       </c>
       <c r="J430" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.25">
@@ -18501,7 +18514,7 @@
         <v>119</v>
       </c>
       <c r="J431" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.25">
@@ -18530,7 +18543,7 @@
         <v>122</v>
       </c>
       <c r="J432" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.25">
@@ -18559,7 +18572,7 @@
         <v>125</v>
       </c>
       <c r="J433" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.25">
@@ -18591,7 +18604,7 @@
         <v>188</v>
       </c>
       <c r="J434" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.25">
@@ -18623,7 +18636,7 @@
         <v>355</v>
       </c>
       <c r="J435" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.25">
@@ -18652,7 +18665,7 @@
         <v>95</v>
       </c>
       <c r="J436" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.25">
@@ -18681,7 +18694,7 @@
         <v>99</v>
       </c>
       <c r="J437" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.25">
@@ -18713,7 +18726,7 @@
         <v>356</v>
       </c>
       <c r="J438" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.25">
@@ -18742,7 +18755,7 @@
         <v>109</v>
       </c>
       <c r="J439" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.25">
@@ -18771,7 +18784,7 @@
         <v>112</v>
       </c>
       <c r="J440" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.25">
@@ -18800,7 +18813,7 @@
         <v>115</v>
       </c>
       <c r="J441" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.25">
@@ -18829,7 +18842,7 @@
         <v>119</v>
       </c>
       <c r="J442" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.25">
@@ -18858,7 +18871,7 @@
         <v>122</v>
       </c>
       <c r="J443" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.25">
@@ -18887,7 +18900,7 @@
         <v>125</v>
       </c>
       <c r="J444" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.25">
@@ -18919,7 +18932,7 @@
         <v>357</v>
       </c>
       <c r="J445" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.25">
@@ -18939,7 +18952,7 @@
         <v>130</v>
       </c>
       <c r="F446" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>98</v>
@@ -18948,7 +18961,7 @@
         <v>132</v>
       </c>
       <c r="J446" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.25">
@@ -18977,7 +18990,7 @@
         <v>132</v>
       </c>
       <c r="J447" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.25">
@@ -19006,7 +19019,7 @@
         <v>128</v>
       </c>
       <c r="J448" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.25">
@@ -19035,7 +19048,7 @@
         <v>128</v>
       </c>
       <c r="J449" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.25">
@@ -19064,7 +19077,7 @@
         <v>151</v>
       </c>
       <c r="J450" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.25">
@@ -19093,7 +19106,7 @@
         <v>151</v>
       </c>
       <c r="J451" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.25">
@@ -19122,7 +19135,7 @@
         <v>158</v>
       </c>
       <c r="J452" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.25">
@@ -19151,7 +19164,7 @@
         <v>161</v>
       </c>
       <c r="J453" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.25">
@@ -19180,7 +19193,7 @@
         <v>161</v>
       </c>
       <c r="J454" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.25">
@@ -19209,7 +19222,7 @@
         <v>161</v>
       </c>
       <c r="J455" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.25">
@@ -19241,7 +19254,7 @@
         <v>361</v>
       </c>
       <c r="J456" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.25">
@@ -19273,7 +19286,7 @@
         <v>362</v>
       </c>
       <c r="J457" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.25">
@@ -19302,7 +19315,7 @@
         <v>95</v>
       </c>
       <c r="J458" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.25">
@@ -19331,7 +19344,7 @@
         <v>99</v>
       </c>
       <c r="J459" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.25">
@@ -19363,7 +19376,7 @@
         <v>363</v>
       </c>
       <c r="J460" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.25">
@@ -19392,7 +19405,7 @@
         <v>109</v>
       </c>
       <c r="J461" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.25">
@@ -19421,7 +19434,7 @@
         <v>112</v>
       </c>
       <c r="J462" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.25">
@@ -19450,7 +19463,7 @@
         <v>115</v>
       </c>
       <c r="J463" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.25">
@@ -19479,7 +19492,7 @@
         <v>119</v>
       </c>
       <c r="J464" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.25">
@@ -19508,7 +19521,7 @@
         <v>122</v>
       </c>
       <c r="J465" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.25">
@@ -19537,7 +19550,7 @@
         <v>125</v>
       </c>
       <c r="J466" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.25">
@@ -19566,7 +19579,7 @@
         <v>161</v>
       </c>
       <c r="J467" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.25">
@@ -19595,7 +19608,7 @@
         <v>161</v>
       </c>
       <c r="J468" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.25">
@@ -19624,7 +19637,7 @@
         <v>161</v>
       </c>
       <c r="J469" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.25">
@@ -19653,7 +19666,7 @@
         <v>86</v>
       </c>
       <c r="J470" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.25">
@@ -19682,7 +19695,7 @@
         <v>90</v>
       </c>
       <c r="J471" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.25">
@@ -19711,7 +19724,7 @@
         <v>95</v>
       </c>
       <c r="J472" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.25">
@@ -19740,7 +19753,7 @@
         <v>99</v>
       </c>
       <c r="J473" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.25">
@@ -19769,7 +19782,7 @@
         <v>103</v>
       </c>
       <c r="J474" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.25">
@@ -19798,7 +19811,7 @@
         <v>109</v>
       </c>
       <c r="J475" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.25">
@@ -19827,7 +19840,7 @@
         <v>112</v>
       </c>
       <c r="J476" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.25">
@@ -19856,7 +19869,7 @@
         <v>115</v>
       </c>
       <c r="J477" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.25">
@@ -19885,7 +19898,7 @@
         <v>119</v>
       </c>
       <c r="J478" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.25">
@@ -19914,7 +19927,7 @@
         <v>122</v>
       </c>
       <c r="J479" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.25">
@@ -19943,7 +19956,7 @@
         <v>125</v>
       </c>
       <c r="J480" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.25">
@@ -19972,7 +19985,7 @@
         <v>86</v>
       </c>
       <c r="J481" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.25">
@@ -20001,7 +20014,7 @@
         <v>90</v>
       </c>
       <c r="J482" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.25">
@@ -20030,7 +20043,7 @@
         <v>95</v>
       </c>
       <c r="J483" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.25">
@@ -20059,7 +20072,7 @@
         <v>99</v>
       </c>
       <c r="J484" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.25">
@@ -20088,7 +20101,7 @@
         <v>103</v>
       </c>
       <c r="J485" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.25">
@@ -20117,7 +20130,7 @@
         <v>109</v>
       </c>
       <c r="J486" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.25">
@@ -20146,7 +20159,7 @@
         <v>112</v>
       </c>
       <c r="J487" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.25">
@@ -20175,7 +20188,7 @@
         <v>115</v>
       </c>
       <c r="J488" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.25">
@@ -20204,7 +20217,7 @@
         <v>119</v>
       </c>
       <c r="J489" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.25">
@@ -20233,7 +20246,7 @@
         <v>122</v>
       </c>
       <c r="J490" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.25">
@@ -20262,7 +20275,7 @@
         <v>125</v>
       </c>
       <c r="J491" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.25">
@@ -20294,7 +20307,7 @@
         <v>222</v>
       </c>
       <c r="J492" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.25">
@@ -20326,7 +20339,7 @@
         <v>370</v>
       </c>
       <c r="J493" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.25">
@@ -20355,7 +20368,7 @@
         <v>95</v>
       </c>
       <c r="J494" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.25">
@@ -20384,7 +20397,7 @@
         <v>99</v>
       </c>
       <c r="J495" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.25">
@@ -20416,7 +20429,7 @@
         <v>371</v>
       </c>
       <c r="J496" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.25">
@@ -20445,7 +20458,7 @@
         <v>109</v>
       </c>
       <c r="J497" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.25">
@@ -20474,7 +20487,7 @@
         <v>112</v>
       </c>
       <c r="J498" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.25">
@@ -20503,7 +20516,7 @@
         <v>115</v>
       </c>
       <c r="J499" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.25">
@@ -20532,7 +20545,7 @@
         <v>119</v>
       </c>
       <c r="J500" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.25">
@@ -20561,7 +20574,7 @@
         <v>122</v>
       </c>
       <c r="J501" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="502" spans="1:10" x14ac:dyDescent="0.25">
@@ -20590,7 +20603,7 @@
         <v>125</v>
       </c>
       <c r="J502" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
   </sheetData>
@@ -20615,30 +20628,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>108</v>
@@ -20646,10 +20659,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>94</v>
@@ -20657,10 +20670,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>94</v>
@@ -20668,10 +20681,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>94</v>
@@ -20679,10 +20692,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>94</v>
@@ -20693,7 +20706,7 @@
         <v>342</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>108</v>
@@ -20710,7 +20723,7 @@
         <v>259</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>108</v>
@@ -20727,7 +20740,7 @@
         <v>282</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>108</v>
@@ -20741,27 +20754,27 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>108</v>
@@ -20772,7 +20785,7 @@
         <v>271</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>108</v>
@@ -20786,10 +20799,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>108</v>
@@ -20797,10 +20810,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>108</v>
@@ -20808,27 +20821,27 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>108</v>
@@ -20836,33 +20849,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -20870,13 +20883,13 @@
         <v>357</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>353</v>
@@ -20889,4 +20902,83 @@
   <autoFilter ref="A1:G19" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>918</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>